--- a/tracking_forms/018_file_record_and_update_form--tracking_forms.xlsx
+++ b/tracking_forms/018_file_record_and_update_form--tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>file_record_and_update_form</t>
+          <t>File Record And Update Form</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>file_version</t>
+          <t>File Version</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>file_date_modified</t>
+          <t>File Date Modified</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>file_update_date</t>
+          <t>File Update Date</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,46 +607,46 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>file_user</t>
+          <t>file_update_status</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>file_user</t>
+          <t>File Update Status</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>file_update_status</t>
+          <t>file_change_details</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>file_update_status</t>
+          <t>File Change Details</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>file_change_details</t>
+          <t>file_update_reason</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>file_change_details</t>
+          <t>File Update Reason</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>file_update_reason</t>
+          <t>file_last_updated_by</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>file_update_reason</t>
+          <t>File Last Updated By</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>file_last_updated_by</t>
+          <t>file_last_update_date</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>file_last_updated_by</t>
+          <t>File Last Update Date</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>file_last_update_date</t>
+          <t>file_last_updated_at</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>file_last_update_date</t>
+          <t>File Last Updated At</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>file_last_updated_at</t>
+          <t>file_last_updated_by_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>file_last_updated_at</t>
+          <t>File Last Updated By 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>file_last_updated_by</t>
+          <t>file_update_comment</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>file_last_updated_by</t>
+          <t>File Update Comment</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>file_update_comment</t>
+          <t>file_last_update_user</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>file_update_comment</t>
+          <t>File Last Update User</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>file_last_update_user</t>
+          <t>file_update_status_updated</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>file_last_update_user</t>
+          <t>File Update Status Updated</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>file_update_status_updated</t>
+          <t>file_user</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>file_update_status_updated</t>
+          <t>File User</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>file_user</t>
+          <t>user_1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>file_user</t>
+          <t>File User 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>file_user</t>
+          <t>last_update_user</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>file_user_1</t>
+          <t>Last Update User</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>file_last_update_user</t>
+          <t>file_update_comment_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>file_last_update_user</t>
+          <t>File Update Comment 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>file_update_comment</t>
+          <t>user_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>file_update_comment</t>
+          <t>File User 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>file_last_updated_by</t>
+          <t>file_last_updated_by_3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>file_last_updated_by</t>
+          <t>File Last Updated By 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -987,8 +987,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'draft'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Draft'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'approved'}</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Approved'}</t>
+          <t>Draft</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'rejected'}</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Rejected'}</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'draft'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Draft'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'approved'}</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Approved'}</t>
+          <t>Draft</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'rejected'}</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Rejected'}</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
